--- a/docs/funding/proposals/in-prep/2026-NSF-PESOSE/nsf-pesose-track1/skp/cherian_coa_template.xlsx
+++ b/docs/funding/proposals/in-prep/2026-NSF-PESOSE/nsf-pesose-track1/skp/cherian_coa_template.xlsx
@@ -2559,7 +2559,11 @@
           <t>Idehen, Endurance</t>
         </is>
       </c>
-      <c r="C63" s="45" t="n"/>
+      <c r="C63" s="45" t="inlineStr">
+        <is>
+          <t>Chorus Innovations, Austin, TX</t>
+        </is>
+      </c>
       <c r="D63" s="10" t="n"/>
       <c r="E63" s="23" t="n"/>
     </row>
@@ -2650,7 +2654,11 @@
           <t>Casals, Andres</t>
         </is>
       </c>
-      <c r="C68" s="45" t="n"/>
+      <c r="C68" s="45" t="inlineStr">
+        <is>
+          <t>Independent, Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
       <c r="D68" s="10" t="n"/>
       <c r="E68" s="23" t="n"/>
     </row>
@@ -2665,7 +2673,11 @@
           <t>Scott, Dominic</t>
         </is>
       </c>
-      <c r="C69" s="45" t="n"/>
+      <c r="C69" s="45" t="inlineStr">
+        <is>
+          <t>Independent, Toronto, Canada</t>
+        </is>
+      </c>
       <c r="D69" s="10" t="n"/>
       <c r="E69" s="23" t="n"/>
     </row>
@@ -2677,10 +2689,14 @@
       </c>
       <c r="B70" s="45" t="inlineStr">
         <is>
-          <t>Scholl, Ben</t>
-        </is>
-      </c>
-      <c r="C70" s="45" t="n"/>
+          <t>Scholl, Benjamin</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>University of Colorado Anschutz, Aurora, CO</t>
+        </is>
+      </c>
       <c r="D70" s="10" t="n"/>
       <c r="E70" s="23" t="n"/>
     </row>
